--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T10:34:48+00:00</t>
+    <t>2026-03-06T12:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:21:15+00:00</t>
+    <t>2026-03-09T10:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
